--- a/clustering/6 subclusters (factoriescap_s (costs) 0 visnorm).xlsx
+++ b/clustering/6 subclusters (factoriescap_s (costs) 0 visnorm).xlsx
@@ -720,18 +720,10 @@
       <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="2">
-        <v>0</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
@@ -758,18 +750,10 @@
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="2">
-        <v>0</v>
-      </c>
-      <c r="C22" s="2">
-        <v>0</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0</v>
-      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
@@ -796,18 +780,10 @@
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="2">
-        <v>0</v>
-      </c>
-      <c r="C24" s="2">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2">
-        <v>0</v>
-      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">

--- a/clustering/6 subclusters (factoriescap_s (costs) 0 visnorm).xlsx
+++ b/clustering/6 subclusters (factoriescap_s (costs) 0 visnorm).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="12">
   <si>
     <t>clust</t>
   </si>
@@ -52,18 +52,22 @@
   </si>
   <si>
     <t>2 (upper)</t>
+  </si>
+  <si>
+    <t>МЕДИАНЫ КЛАСТЕРОВ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,6 +85,15 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -127,7 +140,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -147,6 +160,10 @@
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -164,6 +181,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>396792</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>104774</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5254542" y="104774"/>
+          <a:ext cx="5194383" cy="3724275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -451,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -806,8 +872,129 @@
         <v>2.9449173558643378</v>
       </c>
     </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>0</v>
+      </c>
+      <c r="B31" s="7">
+        <v>10636802.499999991</v>
+      </c>
+      <c r="C31" s="7">
+        <v>27086.06968787999</v>
+      </c>
+      <c r="D31" s="7">
+        <v>225.52620719999959</v>
+      </c>
+      <c r="E31" s="7">
+        <v>24.231622509999639</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>1</v>
+      </c>
+      <c r="B32" s="7">
+        <v>1362810.9999999921</v>
+      </c>
+      <c r="C32" s="7">
+        <v>2961.967007999996</v>
+      </c>
+      <c r="D32" s="7">
+        <v>6.1257419999995282</v>
+      </c>
+      <c r="E32" s="7">
+        <v>4.1264639999997446</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>2</v>
+      </c>
+      <c r="B33" s="7">
+        <v>6730514.9999999972</v>
+      </c>
+      <c r="C33" s="7">
+        <v>55108.17160406</v>
+      </c>
+      <c r="D33" s="7">
+        <v>486.79715012499969</v>
+      </c>
+      <c r="E33" s="7">
+        <v>119.1726239999997</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B7">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C7">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D7">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E7">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:B33">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -819,7 +1006,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C31:C33">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -831,7 +1018,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D31:D33">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -843,7 +1030,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E31:E33">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -857,5 +1044,6 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/clustering/6 subclusters (factoriescap_s (costs) 0 visnorm).xlsx
+++ b/clustering/6 subclusters (factoriescap_s (costs) 0 visnorm).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="11">
   <si>
     <t>clust</t>
   </si>
@@ -53,21 +53,17 @@
   <si>
     <t>2 (upper)</t>
   </si>
-  <si>
-    <t>МЕДИАНЫ КЛАСТЕРОВ</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,15 +81,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -140,15 +127,12 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -160,10 +144,9 @@
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -187,16 +170,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>396792</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>104774</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>235528</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -219,8 +202,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5254542" y="104774"/>
-          <a:ext cx="5194383" cy="3724275"/>
+          <a:off x="5819776" y="228600"/>
+          <a:ext cx="5102802" cy="3381375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -517,14 +500,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -545,104 +527,104 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3">
-        <v>4405292.9999999944</v>
-      </c>
-      <c r="C2" s="3">
-        <v>22701.895940977331</v>
-      </c>
-      <c r="D2" s="3">
-        <v>51.841532443999682</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>434006.87839302112</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1579.083292069754</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1.996193488371792</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1.563010940232314</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1755055.5188627881</v>
+      </c>
+      <c r="C3" s="2">
+        <v>7333.8249003544643</v>
+      </c>
+      <c r="D3" s="2">
+        <v>72.486669298836844</v>
+      </c>
+      <c r="E3" s="2">
+        <v>21.213607428255479</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2566200.428653331</v>
+      </c>
+      <c r="C4" s="2">
+        <v>22123.160946422649</v>
+      </c>
+      <c r="D4" s="2">
+        <v>44.812657046666359</v>
+      </c>
+      <c r="E4" s="2">
         <v>14.690633501332989</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3">
-        <v>15570758.466666659</v>
-      </c>
-      <c r="C3" s="3">
-        <v>33545.799099206663</v>
-      </c>
-      <c r="D3" s="3">
-        <v>578.76217221999968</v>
-      </c>
-      <c r="E3" s="3">
-        <v>108.9785761866664</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
-        <v>704506.70930232143</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1579.083292069753</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1.996193488371792</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1.563010940232314</v>
-      </c>
-    </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3">
-        <v>2894106.2790697631</v>
-      </c>
-      <c r="C5" s="3">
-        <v>7512.2267562567886</v>
-      </c>
-      <c r="D5" s="3">
-        <v>72.852723501627537</v>
-      </c>
-      <c r="E5" s="3">
-        <v>21.67595811197641</v>
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2">
+        <v>9478517.9544400014</v>
+      </c>
+      <c r="C5" s="2">
+        <v>32410.400461065328</v>
+      </c>
+      <c r="D5" s="2">
+        <v>563.12414152133306</v>
+      </c>
+      <c r="E5" s="2">
+        <v>105.1960784693331</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3">
-        <v>5136556.714285709</v>
-      </c>
-      <c r="C6" s="3">
-        <v>51047.885535440713</v>
-      </c>
-      <c r="D6" s="3">
-        <v>369.7237791374996</v>
-      </c>
-      <c r="E6" s="3">
-        <v>71.315231217142539</v>
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2">
+        <v>3302049.889022219</v>
+      </c>
+      <c r="C6" s="2">
+        <v>50168.966231765618</v>
+      </c>
+      <c r="D6" s="2">
+        <v>370.60002533111071</v>
+      </c>
+      <c r="E6" s="2">
+        <v>74.979088384999642</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3">
-        <v>16699820.625</v>
-      </c>
-      <c r="C7" s="3">
-        <v>61554.883061638742</v>
-      </c>
-      <c r="D7" s="3">
-        <v>801.78070272249965</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="A7" s="2">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2">
+        <v>9510502.7182222214</v>
+      </c>
+      <c r="C7" s="2">
+        <v>61554.883061638728</v>
+      </c>
+      <c r="D7" s="2">
+        <v>766.78253021166631</v>
+      </c>
+      <c r="E7" s="2">
         <v>682.80253506187478</v>
       </c>
     </row>
@@ -667,102 +649,102 @@
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <f>C2/$B2</f>
-        <v>5.1533225919314241E-3</v>
-      </c>
-      <c r="D11" s="4">
-        <f t="shared" ref="D11:E11" si="0">D2/$B2</f>
-        <v>1.1768010083324707E-5</v>
-      </c>
-      <c r="E11" s="4">
-        <f t="shared" si="0"/>
-        <v>3.3347687659669875E-6</v>
+        <v>3.6383831010157229E-3</v>
+      </c>
+      <c r="D11" s="3">
+        <f>D2/$C2</f>
+        <v>1.2641470518982686E-3</v>
+      </c>
+      <c r="E11" s="3">
+        <f>E2/$C2</f>
+        <v>9.8982172003329004E-4</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="4">
-        <f t="shared" ref="C12:E12" si="1">C3/$B3</f>
-        <v>2.1544100867674715E-3</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="C12" s="3">
+        <f t="shared" ref="C12:C16" si="0">C3/$B3</f>
+        <v>4.1786854156650923E-3</v>
+      </c>
+      <c r="D12" s="3">
+        <f t="shared" ref="D12:E16" si="1">D3/$C3</f>
+        <v>9.8838832783331599E-3</v>
+      </c>
+      <c r="E12" s="3">
         <f t="shared" si="1"/>
-        <v>3.7169812469893083E-5</v>
-      </c>
-      <c r="E12" s="4">
-        <f t="shared" si="1"/>
-        <v>6.9989253522854371E-6</v>
+        <v>2.8925707548908301E-3</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="4">
-        <f t="shared" ref="C13:E13" si="2">C4/$B4</f>
-        <v>2.2414027733441057E-3</v>
-      </c>
-      <c r="D13" s="4">
-        <f t="shared" si="2"/>
-        <v>2.8334627080395559E-6</v>
-      </c>
-      <c r="E13" s="4">
-        <f t="shared" si="2"/>
-        <v>2.2185891483988507E-6</v>
+      <c r="C13" s="3">
+        <f t="shared" si="0"/>
+        <v>8.6209793667723199E-3</v>
+      </c>
+      <c r="D13" s="3">
+        <f t="shared" si="1"/>
+        <v>2.0255991969317854E-3</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="1"/>
+        <v>6.6403863068710751E-4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="4">
-        <f t="shared" ref="C14:E14" si="3">C5/$B5</f>
-        <v>2.5956983026454035E-3</v>
-      </c>
-      <c r="D14" s="4">
-        <f t="shared" si="3"/>
-        <v>2.5172787892587065E-5</v>
-      </c>
-      <c r="E14" s="4">
-        <f t="shared" si="3"/>
-        <v>7.4896897424733117E-6</v>
+      <c r="C14" s="3">
+        <f t="shared" si="0"/>
+        <v>3.4193531749215494E-3</v>
+      </c>
+      <c r="D14" s="3">
+        <f t="shared" si="1"/>
+        <v>1.7374797395601917E-2</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="1"/>
+        <v>3.2457506532727154E-3</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="4">
-        <f t="shared" ref="C15:E15" si="4">C6/$B6</f>
-        <v>9.9381528083720277E-3</v>
-      </c>
-      <c r="D15" s="4">
-        <f t="shared" si="4"/>
-        <v>7.1978915001411303E-5</v>
-      </c>
-      <c r="E15" s="4">
-        <f t="shared" si="4"/>
-        <v>1.3883859399196696E-5</v>
+      <c r="C15" s="3">
+        <f t="shared" si="0"/>
+        <v>1.5193279301610225E-2</v>
+      </c>
+      <c r="D15" s="3">
+        <f t="shared" si="1"/>
+        <v>7.3870373094603835E-3</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="1"/>
+        <v>1.4945312613901327E-3</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="4">
-        <f t="shared" ref="C16:E16" si="5">C7/$B7</f>
-        <v>3.6859607323859352E-3</v>
-      </c>
-      <c r="D16" s="4">
-        <f t="shared" si="5"/>
-        <v>4.8011336212930108E-5</v>
-      </c>
-      <c r="E16" s="4">
-        <f t="shared" si="5"/>
-        <v>4.0886818511074566E-5</v>
+      <c r="C16" s="3">
+        <f t="shared" si="0"/>
+        <v>6.4723059217152564E-3</v>
+      </c>
+      <c r="D16" s="3">
+        <f t="shared" si="1"/>
+        <v>1.2456891997403997E-2</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="1"/>
+        <v>1.1092581142232731E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -795,21 +777,21 @@
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <f>B3/B2</f>
-        <v>3.534556831217964</v>
-      </c>
-      <c r="C21" s="5">
+        <v>4.0438426353083567</v>
+      </c>
+      <c r="C21" s="4">
         <f>C12/C11</f>
-        <v>0.41806233712995944</v>
-      </c>
-      <c r="D21" s="6">
-        <f t="shared" ref="D21:E21" si="6">D12/D11</f>
-        <v>3.1585469596565674</v>
-      </c>
-      <c r="E21" s="5">
-        <f t="shared" si="6"/>
-        <v>2.0987738111598717</v>
+        <v>1.1485006662708317</v>
+      </c>
+      <c r="D21" s="5">
+        <f t="shared" ref="D21:E21" si="2">D12/D11</f>
+        <v>7.8186183035362236</v>
+      </c>
+      <c r="E21" s="4">
+        <f t="shared" si="2"/>
+        <v>2.9223148940331862</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -825,21 +807,21 @@
       <c r="A23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <f>B5/B4</f>
-        <v>4.107989662633333</v>
-      </c>
-      <c r="C23" s="5">
+        <v>3.6936000199384496</v>
+      </c>
+      <c r="C23" s="4">
         <f>C14/C13</f>
-        <v>1.1580686583931987</v>
-      </c>
-      <c r="D23" s="6">
-        <f t="shared" ref="D23:E23" si="7">D14/D13</f>
-        <v>8.8841077107395083</v>
-      </c>
-      <c r="E23" s="5">
-        <f t="shared" si="7"/>
-        <v>3.375879552948593</v>
+        <v>0.39663163887164593</v>
+      </c>
+      <c r="D23" s="5">
+        <f t="shared" ref="D23:E23" si="3">D14/D13</f>
+        <v>8.5776087500033871</v>
+      </c>
+      <c r="E23" s="4">
+        <f t="shared" si="3"/>
+        <v>4.8878943231272656</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -855,93 +837,88 @@
       <c r="A25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <f>B7/B6</f>
-        <v>3.2511702982962745</v>
-      </c>
-      <c r="C25" s="5">
+        <v>2.8801814139272159</v>
+      </c>
+      <c r="C25" s="4">
         <f>C16/C15</f>
-        <v>0.37088992325423237</v>
-      </c>
-      <c r="D25" s="5">
-        <f t="shared" ref="D25:E25" si="8">D16/D15</f>
-        <v>0.66701944884816255</v>
-      </c>
-      <c r="E25" s="6">
-        <f t="shared" si="8"/>
-        <v>2.9449173558643378</v>
+        <v>0.4259979556243203</v>
+      </c>
+      <c r="D25" s="4">
+        <f t="shared" ref="D25:E25" si="4">D16/D15</f>
+        <v>1.686317731392907</v>
+      </c>
+      <c r="E25" s="5">
+        <f t="shared" si="4"/>
+        <v>7.4221138284621819</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
-        <v>11</v>
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" s="6">
+        <v>797491.199999996</v>
+      </c>
+      <c r="C29" s="6">
+        <v>2931.4503374099941</v>
+      </c>
+      <c r="D29" s="6">
+        <v>6.1222832999997161</v>
+      </c>
+      <c r="E29" s="6">
+        <v>4.0765412699998436</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="A30">
         <v>1</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="B30" s="6">
+        <v>6584465.9638999989</v>
+      </c>
+      <c r="C30" s="6">
+        <v>26626.86386072998</v>
+      </c>
+      <c r="D30" s="6">
+        <v>140.62935851999961</v>
+      </c>
+      <c r="E30" s="6">
+        <v>24.231622509999639</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>2</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>0</v>
-      </c>
-      <c r="B31" s="7">
-        <v>10636802.499999991</v>
-      </c>
-      <c r="C31" s="7">
-        <v>27086.06968787999</v>
-      </c>
-      <c r="D31" s="7">
-        <v>225.52620719999959</v>
-      </c>
-      <c r="E31" s="7">
-        <v>24.231622509999639</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>1</v>
-      </c>
-      <c r="B32" s="7">
-        <v>1362810.9999999921</v>
-      </c>
-      <c r="C32" s="7">
-        <v>2961.967007999996</v>
-      </c>
-      <c r="D32" s="7">
-        <v>6.1257419999995282</v>
-      </c>
-      <c r="E32" s="7">
-        <v>4.1264639999997446</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>2</v>
-      </c>
-      <c r="B33" s="7">
-        <v>6730514.9999999972</v>
-      </c>
-      <c r="C33" s="7">
+      <c r="B31" s="6">
+        <v>4344175.5884999968</v>
+      </c>
+      <c r="C31" s="6">
         <v>55108.17160406</v>
       </c>
-      <c r="D33" s="7">
-        <v>486.79715012499969</v>
-      </c>
-      <c r="E33" s="7">
+      <c r="D31" s="6">
+        <v>486.58164706249948</v>
+      </c>
+      <c r="E31" s="6">
         <v>119.1726239999997</v>
       </c>
     </row>
@@ -994,7 +971,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B33">
+  <conditionalFormatting sqref="B29:B31">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1006,7 +983,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C31:C33">
+  <conditionalFormatting sqref="C29:C31">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1018,7 +995,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D31:D33">
+  <conditionalFormatting sqref="D29:D31">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1030,7 +1007,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E31:E33">
+  <conditionalFormatting sqref="E29:E31">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
